--- a/data/Delete_Employee_Test_Data.xlsx
+++ b/data/Delete_Employee_Test_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ppham\Documents\Do an\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7BFE709-7138-4AC5-B391-921E9CC7647C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{883C919D-1514-402A-8FD4-5F06CFF28095}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3516" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Delete_Data" sheetId="1" r:id="rId1"/>
@@ -454,94 +454,94 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:G5"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="19.88671875" customWidth="1"/>
-    <col min="4" max="4" width="26.33203125" customWidth="1"/>
-    <col min="5" max="5" width="13.88671875" customWidth="1"/>
-    <col min="6" max="6" width="16.6640625" customWidth="1"/>
-    <col min="7" max="7" width="19.21875" customWidth="1"/>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="19.88671875" customWidth="1"/>
+    <col min="3" max="3" width="26.33203125" customWidth="1"/>
+    <col min="4" max="4" width="13.88671875" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" customWidth="1"/>
+    <col min="6" max="6" width="19.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B2" s="2" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B3" s="1" t="s">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="1">
+      <c r="B2" s="1">
         <v>1001</v>
       </c>
+      <c r="C2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1">
+        <v>1010</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="D3" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="1">
-        <v>1010</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="F4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G5" s="1" t="s">
         <v>9</v>
       </c>
     </row>
